--- a/Costo_Beneficio_Marketing_por_Campana_y_Mes_2027.xlsx
+++ b/Costo_Beneficio_Marketing_por_Campana_y_Mes_2027.xlsx
@@ -483,7 +483,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-MX"/>
               </a:p>
@@ -628,7 +628,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-MX"/>
               </a:p>
@@ -776,7 +776,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-MX"/>
           </a:p>
@@ -832,7 +832,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-MX"/>
           </a:p>
@@ -865,7 +865,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-MX"/>
         </a:p>
@@ -975,7 +975,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-MX"/>
               </a:p>
@@ -1117,7 +1117,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-MX"/>
           </a:p>
@@ -1173,7 +1173,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-MX"/>
           </a:p>
@@ -7212,11 +7212,13 @@
       <c r="T1" s="40" t="n"/>
       <c r="U1" s="40" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="C3" s="39" t="n">
         <v>1800000</v>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="17" t="inlineStr">
         <is>
@@ -7337,6 +7339,7 @@
     <row r="8">
       <c r="A8" s="18" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
@@ -7759,7 +7762,7 @@
         </is>
       </c>
       <c r="C16" s="34" t="n">
-        <v>24000000</v>
+        <v>14400000</v>
       </c>
       <c r="D16" s="35" t="n">
         <v>4</v>
@@ -7833,7 +7836,7 @@
         </is>
       </c>
       <c r="C17" s="34" t="n">
-        <v>8000000</v>
+        <v>4800000</v>
       </c>
       <c r="D17" s="35" t="n">
         <v>5</v>
@@ -8308,6 +8311,7 @@
       </c>
       <c r="U23" s="13" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="18" t="n"/>
     </row>
